--- a/Camera/CDH30235081704773-1/CDH30235081704773-1.xlsx
+++ b/Camera/CDH30235081704773-1/CDH30235081704773-1.xlsx
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>相机</t>
+          <t>摄像头</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
